--- a/data/ffallone.xlsx
+++ b/data/ffallone.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/Resumen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{3875612B-0CD9-4688-B0A0-9EAA8950F35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D17220B-F814-4754-9A22-3419A2794562}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{3875612B-0CD9-4688-B0A0-9EAA8950F35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE4B81C6-2107-4E0D-AA29-FA1858ACFA74}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2DB1EEB4-5F51-4BE5-AC0C-E3E1204924FB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="17">
   <si>
     <t>Fecha</t>
   </si>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE7E66C-4ADF-4C77-9F5D-2989E1F1BC2C}">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
@@ -2954,29 +2954,189 @@
         <v>15</v>
       </c>
       <c r="D61" s="4">
-        <f t="shared" ref="D61" si="70">+D60+K60+E60-F61</f>
+        <f t="shared" ref="D61:D65" si="70">+D60+K60+E60-F61</f>
         <v>294084.89</v>
+      </c>
+      <c r="G61" s="4">
+        <v>4117.1899999999996</v>
       </c>
       <c r="H61" s="5">
         <f t="shared" si="65"/>
-        <v>180836.00000000006</v>
+        <v>184953.19000000006</v>
       </c>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
       <c r="K61" s="5">
         <f t="shared" si="66"/>
-        <v>0</v>
+        <v>4117.1899999999996</v>
       </c>
       <c r="L61" s="5">
         <f t="shared" si="67"/>
-        <v>180836.00000000006</v>
+        <v>184953.19000000006</v>
       </c>
       <c r="M61" s="5">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>137.23966666666666</v>
       </c>
       <c r="N61" s="6">
         <f t="shared" si="69"/>
+        <v>1.4000005236583218E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="3">
+        <v>45901</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="4">
+        <f t="shared" si="70"/>
+        <v>298202.08</v>
+      </c>
+      <c r="G62" s="4">
+        <v>6858.65</v>
+      </c>
+      <c r="H62" s="5">
+        <f t="shared" ref="H62:H65" si="71">+H61+G62</f>
+        <v>191811.84000000005</v>
+      </c>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5">
+        <f t="shared" ref="K62:K65" si="72">+G62-I62</f>
+        <v>6858.65</v>
+      </c>
+      <c r="L62" s="5">
+        <f t="shared" ref="L62:L65" si="73">+L61+K62</f>
+        <v>191811.84000000005</v>
+      </c>
+      <c r="M62" s="5">
+        <f t="shared" ref="M62:M65" si="74">+K62/30</f>
+        <v>228.62166666666664</v>
+      </c>
+      <c r="N62" s="6">
+        <f t="shared" ref="N62:N65" si="75">+G62/D62</f>
+        <v>2.3000007243410239E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="3">
+        <v>45931</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="4">
+        <f t="shared" si="70"/>
+        <v>305060.73000000004</v>
+      </c>
+      <c r="G63" s="4">
+        <v>6406.27</v>
+      </c>
+      <c r="H63" s="5">
+        <f t="shared" si="71"/>
+        <v>198218.11000000004</v>
+      </c>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5">
+        <f t="shared" si="72"/>
+        <v>6406.27</v>
+      </c>
+      <c r="L63" s="5">
+        <f t="shared" si="73"/>
+        <v>198218.11000000004</v>
+      </c>
+      <c r="M63" s="5">
+        <f t="shared" si="74"/>
+        <v>213.54233333333335</v>
+      </c>
+      <c r="N63" s="6">
+        <f t="shared" si="75"/>
+        <v>2.0999982528069082E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
+        <v>45962</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="4">
+        <f t="shared" si="70"/>
+        <v>311467.00000000006</v>
+      </c>
+      <c r="G64" s="4">
+        <v>11212.81</v>
+      </c>
+      <c r="H64" s="5">
+        <f t="shared" si="71"/>
+        <v>209430.92000000004</v>
+      </c>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5">
+        <f t="shared" si="72"/>
+        <v>11212.81</v>
+      </c>
+      <c r="L64" s="5">
+        <f t="shared" si="73"/>
+        <v>209430.92000000004</v>
+      </c>
+      <c r="M64" s="5">
+        <f t="shared" si="74"/>
+        <v>373.76033333333334</v>
+      </c>
+      <c r="N64" s="6">
+        <f t="shared" si="75"/>
+        <v>3.5999993578773988E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="3">
+        <v>45992</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="4">
+        <f t="shared" si="70"/>
+        <v>322679.81000000006</v>
+      </c>
+      <c r="H65" s="5">
+        <f t="shared" si="71"/>
+        <v>209430.92000000004</v>
+      </c>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="L65" s="5">
+        <f t="shared" si="73"/>
+        <v>209430.92000000004</v>
+      </c>
+      <c r="M65" s="5">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="N65" s="6">
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
     </row>

--- a/data/ffallone.xlsx
+++ b/data/ffallone.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Documentos\Proyectos\FIFI\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/Proyectos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2393848D-C888-41F4-B81B-43F2BB25DFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{2393848D-C888-41F4-B81B-43F2BB25DFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B647237-D6E3-4B0B-BFAC-2B843174FC51}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{2DB1EEB4-5F51-4BE5-AC0C-E3E1204924FB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="17">
   <si>
     <t>Fecha</t>
   </si>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE7E66C-4ADF-4C77-9F5D-2989E1F1BC2C}">
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
@@ -3237,27 +3237,150 @@
         <f t="shared" si="76"/>
         <v>340906.93000000011</v>
       </c>
+      <c r="G68" s="4">
+        <v>4401.1400000000003</v>
+      </c>
       <c r="H68" s="5">
         <f t="shared" si="77"/>
-        <v>227658.04000000007</v>
+        <v>232059.18000000008</v>
       </c>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
       <c r="K68" s="5">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>4401.1400000000003</v>
       </c>
       <c r="L68" s="5">
         <f t="shared" si="79"/>
-        <v>227658.04000000007</v>
+        <v>232059.18000000008</v>
       </c>
       <c r="M68" s="5">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>146.70466666666667</v>
       </c>
       <c r="N68" s="6">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>1.2910092499439653E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" s="3">
+        <v>46113</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="4">
+        <f t="shared" ref="D69:D71" si="82">+D68+K68+E68-F69</f>
+        <v>345308.07000000012</v>
+      </c>
+      <c r="G69" s="4">
+        <v>2300</v>
+      </c>
+      <c r="H69" s="5">
+        <f t="shared" ref="H69:H71" si="83">+H68+G69</f>
+        <v>234359.18000000008</v>
+      </c>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5">
+        <f t="shared" ref="K69:K71" si="84">+G69-I69</f>
+        <v>2300</v>
+      </c>
+      <c r="L69" s="5">
+        <f t="shared" ref="L69:L71" si="85">+L68+K69</f>
+        <v>234359.18000000008</v>
+      </c>
+      <c r="M69" s="5">
+        <f t="shared" ref="M69:M71" si="86">+K69/30</f>
+        <v>76.666666666666671</v>
+      </c>
+      <c r="N69" s="6">
+        <f t="shared" ref="N69:N71" si="87">+G69/D69</f>
+        <v>6.6607189342548501E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A70" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="4">
+        <f t="shared" si="82"/>
+        <v>347608.07000000012</v>
+      </c>
+      <c r="G70" s="4">
+        <v>8250.41</v>
+      </c>
+      <c r="H70" s="5">
+        <f t="shared" si="83"/>
+        <v>242609.59000000008</v>
+      </c>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5">
+        <f t="shared" si="84"/>
+        <v>8250.41</v>
+      </c>
+      <c r="L70" s="5">
+        <f t="shared" si="85"/>
+        <v>242609.59000000008</v>
+      </c>
+      <c r="M70" s="5">
+        <f t="shared" si="86"/>
+        <v>275.01366666666667</v>
+      </c>
+      <c r="N70" s="6">
+        <f t="shared" si="87"/>
+        <v>2.3734805696542075E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" s="4">
+        <f t="shared" si="82"/>
+        <v>355858.4800000001</v>
+      </c>
+      <c r="G71" s="4">
+        <v>6489.89</v>
+      </c>
+      <c r="H71" s="5">
+        <f t="shared" si="83"/>
+        <v>249099.4800000001</v>
+      </c>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5">
+        <f t="shared" si="84"/>
+        <v>6489.89</v>
+      </c>
+      <c r="L71" s="5">
+        <f t="shared" si="85"/>
+        <v>249099.4800000001</v>
+      </c>
+      <c r="M71" s="5">
+        <f t="shared" si="86"/>
+        <v>216.32966666666667</v>
+      </c>
+      <c r="N71" s="6">
+        <f t="shared" si="87"/>
+        <v>1.8237277920143981E-2</v>
       </c>
     </row>
   </sheetData>
